--- a/signal_coodination/experiment_with_offsets_filtered_cum.xlsx
+++ b/signal_coodination/experiment_with_offsets_filtered_cum.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:U157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,36 +534,6 @@
           <t>TTT(s/veh)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>d0_stop(s/veh)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>d1_stop(s/veh)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>d2_stop(s/veh)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>d3_stop(s/veh)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>d_stop_total(s/veh)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Nveh_total_eval</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -600,13 +570,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>116.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>58.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>86.39999999999999</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -621,31 +591,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>47.99999999999945</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>96.00000000000003</v>
+        <v>7.407407407407406</v>
       </c>
       <c r="U2" t="n">
-        <v>143.9999999999995</v>
-      </c>
-      <c r="V2" t="n">
-        <v>21.12000000000002</v>
-      </c>
-      <c r="W2" t="n">
-        <v>24.48000000000001</v>
-      </c>
-      <c r="X2" t="n">
-        <v>30.864</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.600000000000014</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>78.06400000000005</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>180</v>
+        <v>7.407407407407406</v>
       </c>
     </row>
     <row r="3">
@@ -712,12 +664,6 @@
       <c r="U3" t="n">
         <v>7.797270955165691</v>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -783,12 +729,6 @@
       <c r="U4" t="n">
         <v>8.2304526748971</v>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -854,12 +794,6 @@
       <c r="U5" t="n">
         <v>8.714596949891046</v>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -925,12 +859,6 @@
       <c r="U6" t="n">
         <v>9.259259259259236</v>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -996,12 +924,6 @@
       <c r="U7" t="n">
         <v>9.876543209876521</v>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1067,12 +989,6 @@
       <c r="U8" t="n">
         <v>10.58201058201056</v>
       </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1138,12 +1054,6 @@
       <c r="U9" t="n">
         <v>11.39601139601137</v>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1209,12 +1119,6 @@
       <c r="U10" t="n">
         <v>12.34567901234565</v>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1280,12 +1184,6 @@
       <c r="U11" t="n">
         <v>13.46801346801344</v>
       </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1351,12 +1249,6 @@
       <c r="U12" t="n">
         <v>14.81481481481478</v>
       </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1422,12 +1314,6 @@
       <c r="U13" t="n">
         <v>16.4609053497942</v>
       </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1493,12 +1379,6 @@
       <c r="U14" t="n">
         <v>18.51851851851847</v>
       </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1564,12 +1444,6 @@
       <c r="U15" t="n">
         <v>9.259259259259261</v>
       </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1635,12 +1509,6 @@
       <c r="U16" t="n">
         <v>9.746588693957118</v>
       </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1706,12 +1574,6 @@
       <c r="U17" t="n">
         <v>10.2880658436214</v>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1777,12 +1639,6 @@
       <c r="U18" t="n">
         <v>10.89324618736384</v>
       </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1848,12 +1704,6 @@
       <c r="U19" t="n">
         <v>11.57407407407408</v>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1919,12 +1769,6 @@
       <c r="U20" t="n">
         <v>12.34567901234568</v>
       </c>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1990,12 +1834,6 @@
       <c r="U21" t="n">
         <v>13.22751322751323</v>
       </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2061,12 +1899,6 @@
       <c r="U22" t="n">
         <v>14.24501424501425</v>
       </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2132,12 +1964,6 @@
       <c r="U23" t="n">
         <v>15.4320987654321</v>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2203,12 +2029,6 @@
       <c r="U24" t="n">
         <v>16.83501683501684</v>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2274,12 +2094,6 @@
       <c r="U25" t="n">
         <v>18.51851851851852</v>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2345,12 +2159,6 @@
       <c r="U26" t="n">
         <v>20.5761316872428</v>
       </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2416,12 +2224,6 @@
       <c r="U27" t="n">
         <v>23.14814814814815</v>
       </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2487,12 +2289,6 @@
       <c r="U28" t="n">
         <v>11.11111111111111</v>
       </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2558,12 +2354,6 @@
       <c r="U29" t="n">
         <v>11.69590643274854</v>
       </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2629,12 +2419,6 @@
       <c r="U30" t="n">
         <v>12.34567901234568</v>
       </c>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2700,12 +2484,6 @@
       <c r="U31" t="n">
         <v>13.0718954248366</v>
       </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2771,12 +2549,6 @@
       <c r="U32" t="n">
         <v>13.88888888888889</v>
       </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2842,12 +2614,6 @@
       <c r="U33" t="n">
         <v>14.81481481481481</v>
       </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2913,12 +2679,6 @@
       <c r="U34" t="n">
         <v>15.87301587301587</v>
       </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2984,12 +2744,6 @@
       <c r="U35" t="n">
         <v>17.09401709401709</v>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3055,12 +2809,6 @@
       <c r="U36" t="n">
         <v>18.51851851851852</v>
       </c>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3126,12 +2874,6 @@
       <c r="U37" t="n">
         <v>20.2020202020202</v>
       </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3197,12 +2939,6 @@
       <c r="U38" t="n">
         <v>22.22222222222222</v>
       </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3268,12 +3004,6 @@
       <c r="U39" t="n">
         <v>24.69135802469136</v>
       </c>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3339,12 +3069,6 @@
       <c r="U40" t="n">
         <v>27.77777777777778</v>
       </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3410,12 +3134,6 @@
       <c r="U41" t="n">
         <v>7.407407407407408</v>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3481,12 +3199,6 @@
       <c r="U42" t="n">
         <v>7.797270955165692</v>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3552,12 +3264,6 @@
       <c r="U43" t="n">
         <v>8.230452674897121</v>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3623,12 +3329,6 @@
       <c r="U44" t="n">
         <v>8.714596949891069</v>
       </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3694,12 +3394,6 @@
       <c r="U45" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3765,12 +3459,6 @@
       <c r="U46" t="n">
         <v>9.876543209876543</v>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3836,12 +3524,6 @@
       <c r="U47" t="n">
         <v>10.58201058201058</v>
       </c>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3907,12 +3589,6 @@
       <c r="U48" t="n">
         <v>11.3960113960114</v>
       </c>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3978,12 +3654,6 @@
       <c r="U49" t="n">
         <v>12.34567901234568</v>
       </c>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4049,12 +3719,6 @@
       <c r="U50" t="n">
         <v>13.46801346801347</v>
       </c>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4120,12 +3784,6 @@
       <c r="U51" t="n">
         <v>14.81481481481482</v>
       </c>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4191,12 +3849,6 @@
       <c r="U52" t="n">
         <v>16.46090534979424</v>
       </c>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4262,12 +3914,6 @@
       <c r="U53" t="n">
         <v>18.51851851851852</v>
       </c>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4333,12 +3979,6 @@
       <c r="U54" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4404,12 +4044,6 @@
       <c r="U55" t="n">
         <v>9.746588693957117</v>
       </c>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4475,12 +4109,6 @@
       <c r="U56" t="n">
         <v>10.2880658436214</v>
       </c>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4546,12 +4174,6 @@
       <c r="U57" t="n">
         <v>10.89324618736383</v>
       </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4617,12 +4239,6 @@
       <c r="U58" t="n">
         <v>11.57407407407408</v>
       </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4688,12 +4304,6 @@
       <c r="U59" t="n">
         <v>12.34567901234568</v>
       </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4759,12 +4369,6 @@
       <c r="U60" t="n">
         <v>13.22751322751323</v>
       </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4830,12 +4434,6 @@
       <c r="U61" t="n">
         <v>14.24501424501424</v>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4901,12 +4499,6 @@
       <c r="U62" t="n">
         <v>15.4320987654321</v>
       </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4972,12 +4564,6 @@
       <c r="U63" t="n">
         <v>16.83501683501683</v>
       </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5043,12 +4629,6 @@
       <c r="U64" t="n">
         <v>18.51851851851852</v>
       </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5114,12 +4694,6 @@
       <c r="U65" t="n">
         <v>20.5761316872428</v>
       </c>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5185,12 +4759,6 @@
       <c r="U66" t="n">
         <v>23.14814814814815</v>
       </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5256,12 +4824,6 @@
       <c r="U67" t="n">
         <v>11.11111111111111</v>
       </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5327,12 +4889,6 @@
       <c r="U68" t="n">
         <v>11.69590643274854</v>
       </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5398,12 +4954,6 @@
       <c r="U69" t="n">
         <v>12.34567901234568</v>
       </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5469,12 +5019,6 @@
       <c r="U70" t="n">
         <v>13.0718954248366</v>
       </c>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5540,12 +5084,6 @@
       <c r="U71" t="n">
         <v>13.88888888888889</v>
       </c>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5611,12 +5149,6 @@
       <c r="U72" t="n">
         <v>14.81481481481481</v>
       </c>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5682,12 +5214,6 @@
       <c r="U73" t="n">
         <v>15.87301587301587</v>
       </c>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5753,12 +5279,6 @@
       <c r="U74" t="n">
         <v>17.09401709401709</v>
       </c>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5824,12 +5344,6 @@
       <c r="U75" t="n">
         <v>18.51851851851852</v>
       </c>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5895,12 +5409,6 @@
       <c r="U76" t="n">
         <v>20.2020202020202</v>
       </c>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5966,12 +5474,6 @@
       <c r="U77" t="n">
         <v>22.22222222222222</v>
       </c>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6037,12 +5539,6 @@
       <c r="U78" t="n">
         <v>24.69135802469136</v>
       </c>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6108,12 +5604,6 @@
       <c r="U79" t="n">
         <v>27.77777777777778</v>
       </c>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6179,12 +5669,6 @@
       <c r="U80" t="n">
         <v>12.96296296296296</v>
       </c>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6250,12 +5734,6 @@
       <c r="U81" t="n">
         <v>13.64522417153996</v>
       </c>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6321,12 +5799,6 @@
       <c r="U82" t="n">
         <v>14.40329218106996</v>
       </c>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6392,12 +5864,6 @@
       <c r="U83" t="n">
         <v>15.25054466230937</v>
       </c>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6463,12 +5929,6 @@
       <c r="U84" t="n">
         <v>16.20370370370371</v>
       </c>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6534,12 +5994,6 @@
       <c r="U85" t="n">
         <v>17.28395061728395</v>
       </c>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6605,12 +6059,6 @@
       <c r="U86" t="n">
         <v>18.51851851851852</v>
       </c>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6676,12 +6124,6 @@
       <c r="U87" t="n">
         <v>19.94301994301994</v>
       </c>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6747,12 +6189,6 @@
       <c r="U88" t="n">
         <v>21.60493827160494</v>
       </c>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6818,12 +6254,6 @@
       <c r="U89" t="n">
         <v>23.56902356902357</v>
       </c>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6889,12 +6319,6 @@
       <c r="U90" t="n">
         <v>25.92592592592593</v>
       </c>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6960,12 +6384,6 @@
       <c r="U91" t="n">
         <v>28.80658436213992</v>
       </c>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7031,12 +6449,6 @@
       <c r="U92" t="n">
         <v>32.40740740740741</v>
       </c>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7102,12 +6514,6 @@
       <c r="U93" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7173,12 +6579,6 @@
       <c r="U94" t="n">
         <v>9.746588693957117</v>
       </c>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7244,12 +6644,6 @@
       <c r="U95" t="n">
         <v>10.2880658436214</v>
       </c>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7315,12 +6709,6 @@
       <c r="U96" t="n">
         <v>10.89324618736383</v>
       </c>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7386,12 +6774,6 @@
       <c r="U97" t="n">
         <v>11.57407407407408</v>
       </c>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7457,12 +6839,6 @@
       <c r="U98" t="n">
         <v>12.34567901234568</v>
       </c>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7528,12 +6904,6 @@
       <c r="U99" t="n">
         <v>13.22751322751323</v>
       </c>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7599,12 +6969,6 @@
       <c r="U100" t="n">
         <v>14.24501424501424</v>
       </c>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
-      <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7670,12 +7034,6 @@
       <c r="U101" t="n">
         <v>15.4320987654321</v>
       </c>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7741,12 +7099,6 @@
       <c r="U102" t="n">
         <v>16.83501683501683</v>
       </c>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
-      <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7812,12 +7164,6 @@
       <c r="U103" t="n">
         <v>18.51851851851852</v>
       </c>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
-      <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7883,12 +7229,6 @@
       <c r="U104" t="n">
         <v>20.5761316872428</v>
       </c>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7954,12 +7294,6 @@
       <c r="U105" t="n">
         <v>23.14814814814815</v>
       </c>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr"/>
-      <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8025,12 +7359,6 @@
       <c r="U106" t="n">
         <v>6.944444444444445</v>
       </c>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8096,12 +7424,6 @@
       <c r="U107" t="n">
         <v>7.309941520467836</v>
       </c>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8167,12 +7489,6 @@
       <c r="U108" t="n">
         <v>7.716049382716049</v>
       </c>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8238,12 +7554,6 @@
       <c r="U109" t="n">
         <v>8.169934640522875</v>
       </c>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr"/>
-      <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8309,12 +7619,6 @@
       <c r="U110" t="n">
         <v>8.680555555555555</v>
       </c>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
-      <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8380,12 +7684,6 @@
       <c r="U111" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
-      <c r="Y111" t="inlineStr"/>
-      <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8451,12 +7749,6 @@
       <c r="U112" t="n">
         <v>9.920634920634921</v>
       </c>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8522,12 +7814,6 @@
       <c r="U113" t="n">
         <v>10.68376068376068</v>
       </c>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
-      <c r="Y113" t="inlineStr"/>
-      <c r="Z113" t="inlineStr"/>
-      <c r="AA113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8593,12 +7879,6 @@
       <c r="U114" t="n">
         <v>11.57407407407407</v>
       </c>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr"/>
-      <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8664,12 +7944,6 @@
       <c r="U115" t="n">
         <v>12.62626262626263</v>
       </c>
-      <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
-      <c r="Y115" t="inlineStr"/>
-      <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8735,12 +8009,6 @@
       <c r="U116" t="n">
         <v>13.88888888888889</v>
       </c>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
-      <c r="Y116" t="inlineStr"/>
-      <c r="Z116" t="inlineStr"/>
-      <c r="AA116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8806,12 +8074,6 @@
       <c r="U117" t="n">
         <v>15.4320987654321</v>
       </c>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr"/>
-      <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8877,12 +8139,6 @@
       <c r="U118" t="n">
         <v>17.36111111111111</v>
       </c>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
-      <c r="Y118" t="inlineStr"/>
-      <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8948,12 +8204,6 @@
       <c r="U119" t="n">
         <v>8.796296296296298</v>
       </c>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
-      <c r="Y119" t="inlineStr"/>
-      <c r="Z119" t="inlineStr"/>
-      <c r="AA119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9019,12 +8269,6 @@
       <c r="U120" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
-      <c r="Y120" t="inlineStr"/>
-      <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9090,12 +8334,6 @@
       <c r="U121" t="n">
         <v>9.77366255144033</v>
       </c>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
-      <c r="Y121" t="inlineStr"/>
-      <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9161,12 +8399,6 @@
       <c r="U122" t="n">
         <v>10.34858387799564</v>
       </c>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
-      <c r="Y122" t="inlineStr"/>
-      <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9232,12 +8464,6 @@
       <c r="U123" t="n">
         <v>10.99537037037037</v>
       </c>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
-      <c r="Y123" t="inlineStr"/>
-      <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9303,12 +8529,6 @@
       <c r="U124" t="n">
         <v>11.7283950617284</v>
       </c>
-      <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
-      <c r="Y124" t="inlineStr"/>
-      <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9374,12 +8594,6 @@
       <c r="U125" t="n">
         <v>12.56613756613757</v>
       </c>
-      <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9445,12 +8659,6 @@
       <c r="U126" t="n">
         <v>13.53276353276354</v>
       </c>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr"/>
-      <c r="Y126" t="inlineStr"/>
-      <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9516,12 +8724,6 @@
       <c r="U127" t="n">
         <v>14.6604938271605</v>
       </c>
-      <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
-      <c r="X127" t="inlineStr"/>
-      <c r="Y127" t="inlineStr"/>
-      <c r="Z127" t="inlineStr"/>
-      <c r="AA127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9587,12 +8789,6 @@
       <c r="U128" t="n">
         <v>15.99326599326599</v>
       </c>
-      <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
-      <c r="Y128" t="inlineStr"/>
-      <c r="Z128" t="inlineStr"/>
-      <c r="AA128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9658,12 +8854,6 @@
       <c r="U129" t="n">
         <v>17.5925925925926</v>
       </c>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="inlineStr"/>
-      <c r="Z129" t="inlineStr"/>
-      <c r="AA129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9729,12 +8919,6 @@
       <c r="U130" t="n">
         <v>19.54732510288066</v>
       </c>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
-      <c r="X130" t="inlineStr"/>
-      <c r="Y130" t="inlineStr"/>
-      <c r="Z130" t="inlineStr"/>
-      <c r="AA130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9800,12 +8984,6 @@
       <c r="U131" t="n">
         <v>21.99074074074074</v>
       </c>
-      <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
-      <c r="Y131" t="inlineStr"/>
-      <c r="Z131" t="inlineStr"/>
-      <c r="AA131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9871,12 +9049,6 @@
       <c r="U132" t="n">
         <v>10.64814814814815</v>
       </c>
-      <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
-      <c r="Y132" t="inlineStr"/>
-      <c r="Z132" t="inlineStr"/>
-      <c r="AA132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9942,12 +9114,6 @@
       <c r="U133" t="n">
         <v>11.20857699805068</v>
       </c>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
-      <c r="Y133" t="inlineStr"/>
-      <c r="Z133" t="inlineStr"/>
-      <c r="AA133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10013,12 +9179,6 @@
       <c r="U134" t="n">
         <v>11.83127572016461</v>
       </c>
-      <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
-      <c r="Y134" t="inlineStr"/>
-      <c r="Z134" t="inlineStr"/>
-      <c r="AA134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10084,12 +9244,6 @@
       <c r="U135" t="n">
         <v>12.52723311546841</v>
       </c>
-      <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
-      <c r="Y135" t="inlineStr"/>
-      <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10155,12 +9309,6 @@
       <c r="U136" t="n">
         <v>13.31018518518519</v>
       </c>
-      <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
-      <c r="Y136" t="inlineStr"/>
-      <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10226,12 +9374,6 @@
       <c r="U137" t="n">
         <v>14.19753086419753</v>
       </c>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
-      <c r="X137" t="inlineStr"/>
-      <c r="Y137" t="inlineStr"/>
-      <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10297,12 +9439,6 @@
       <c r="U138" t="n">
         <v>15.21164021164021</v>
       </c>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
-      <c r="Y138" t="inlineStr"/>
-      <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10368,12 +9504,6 @@
       <c r="U139" t="n">
         <v>16.38176638176638</v>
       </c>
-      <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
-      <c r="Y139" t="inlineStr"/>
-      <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10439,12 +9569,6 @@
       <c r="U140" t="n">
         <v>17.74691358024691</v>
       </c>
-      <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
-      <c r="Y140" t="inlineStr"/>
-      <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10510,12 +9634,6 @@
       <c r="U141" t="n">
         <v>19.36026936026936</v>
       </c>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
-      <c r="Y141" t="inlineStr"/>
-      <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10581,12 +9699,6 @@
       <c r="U142" t="n">
         <v>21.2962962962963</v>
       </c>
-      <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
-      <c r="Y142" t="inlineStr"/>
-      <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10652,12 +9764,6 @@
       <c r="U143" t="n">
         <v>23.66255144032922</v>
       </c>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr"/>
-      <c r="Y143" t="inlineStr"/>
-      <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10723,12 +9829,6 @@
       <c r="U144" t="n">
         <v>26.62037037037037</v>
       </c>
-      <c r="V144" t="inlineStr"/>
-      <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
-      <c r="Y144" t="inlineStr"/>
-      <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -10794,12 +9894,6 @@
       <c r="U145" t="n">
         <v>8.796296296296298</v>
       </c>
-      <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr"/>
-      <c r="X145" t="inlineStr"/>
-      <c r="Y145" t="inlineStr"/>
-      <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10865,12 +9959,6 @@
       <c r="U146" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr"/>
-      <c r="Y146" t="inlineStr"/>
-      <c r="Z146" t="inlineStr"/>
-      <c r="AA146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10936,12 +10024,6 @@
       <c r="U147" t="n">
         <v>9.77366255144033</v>
       </c>
-      <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
-      <c r="Y147" t="inlineStr"/>
-      <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11007,12 +10089,6 @@
       <c r="U148" t="n">
         <v>10.34858387799564</v>
       </c>
-      <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr"/>
-      <c r="Y148" t="inlineStr"/>
-      <c r="Z148" t="inlineStr"/>
-      <c r="AA148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11078,12 +10154,6 @@
       <c r="U149" t="n">
         <v>10.99537037037037</v>
       </c>
-      <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
-      <c r="X149" t="inlineStr"/>
-      <c r="Y149" t="inlineStr"/>
-      <c r="Z149" t="inlineStr"/>
-      <c r="AA149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11149,12 +10219,6 @@
       <c r="U150" t="n">
         <v>11.7283950617284</v>
       </c>
-      <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
-      <c r="X150" t="inlineStr"/>
-      <c r="Y150" t="inlineStr"/>
-      <c r="Z150" t="inlineStr"/>
-      <c r="AA150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11220,12 +10284,6 @@
       <c r="U151" t="n">
         <v>12.56613756613757</v>
       </c>
-      <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
-      <c r="X151" t="inlineStr"/>
-      <c r="Y151" t="inlineStr"/>
-      <c r="Z151" t="inlineStr"/>
-      <c r="AA151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -11291,12 +10349,6 @@
       <c r="U152" t="n">
         <v>13.53276353276354</v>
       </c>
-      <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
-      <c r="X152" t="inlineStr"/>
-      <c r="Y152" t="inlineStr"/>
-      <c r="Z152" t="inlineStr"/>
-      <c r="AA152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -11362,12 +10414,6 @@
       <c r="U153" t="n">
         <v>14.6604938271605</v>
       </c>
-      <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
-      <c r="Y153" t="inlineStr"/>
-      <c r="Z153" t="inlineStr"/>
-      <c r="AA153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -11433,12 +10479,6 @@
       <c r="U154" t="n">
         <v>15.99326599326599</v>
       </c>
-      <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr"/>
-      <c r="Y154" t="inlineStr"/>
-      <c r="Z154" t="inlineStr"/>
-      <c r="AA154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -11504,12 +10544,6 @@
       <c r="U155" t="n">
         <v>17.5925925925926</v>
       </c>
-      <c r="V155" t="inlineStr"/>
-      <c r="W155" t="inlineStr"/>
-      <c r="X155" t="inlineStr"/>
-      <c r="Y155" t="inlineStr"/>
-      <c r="Z155" t="inlineStr"/>
-      <c r="AA155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -11575,12 +10609,6 @@
       <c r="U156" t="n">
         <v>19.54732510288066</v>
       </c>
-      <c r="V156" t="inlineStr"/>
-      <c r="W156" t="inlineStr"/>
-      <c r="X156" t="inlineStr"/>
-      <c r="Y156" t="inlineStr"/>
-      <c r="Z156" t="inlineStr"/>
-      <c r="AA156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -11646,12 +10674,6 @@
       <c r="U157" t="n">
         <v>21.99074074074074</v>
       </c>
-      <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
-      <c r="X157" t="inlineStr"/>
-      <c r="Y157" t="inlineStr"/>
-      <c r="Z157" t="inlineStr"/>
-      <c r="AA157" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
